--- a/JsonConverter/ExcelFiles/DropTableData.xlsx
+++ b/JsonConverter/ExcelFiles/DropTableData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -92,6 +92,24 @@
   </si>
   <si>
     <t>item_cowbombie_badge_01</t>
+  </si>
+  <si>
+    <t>droptable_maxikeleton_01</t>
+  </si>
+  <si>
+    <t>item_maxikeleton_hat_01</t>
+  </si>
+  <si>
+    <t>item_maxikeleton_guitar_01</t>
+  </si>
+  <si>
+    <t>droptable_deserteagle_01</t>
+  </si>
+  <si>
+    <t>item_deserteagle_feather_01</t>
+  </si>
+  <si>
+    <t>item_deserteagle_diamond_01</t>
   </si>
 </sst>
 </file>
@@ -186,10 +204,10 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -412,13 +430,14 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.0"/>
+    <col customWidth="1" min="1" max="1" width="21.63"/>
     <col customWidth="1" min="2" max="2" width="14.63"/>
     <col customWidth="1" min="3" max="3" width="19.5"/>
-    <col customWidth="1" min="4" max="4" width="17.75"/>
-    <col customWidth="1" min="5" max="5" width="16.75"/>
-    <col customWidth="1" min="6" max="6" width="19.13"/>
-    <col customWidth="1" min="7" max="26" width="11.0"/>
+    <col customWidth="1" min="4" max="4" width="20.63"/>
+    <col customWidth="1" min="5" max="5" width="19.88"/>
+    <col customWidth="1" min="6" max="6" width="22.0"/>
+    <col customWidth="1" min="7" max="7" width="14.0"/>
+    <col customWidth="1" min="8" max="26" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -566,8 +585,8 @@
       <c r="B4" s="1">
         <v>1.0</v>
       </c>
-      <c r="C4" s="1">
-        <v>5.0</v>
+      <c r="C4" s="6">
+        <v>4.0</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>22</v>
@@ -575,7 +594,7 @@
       <c r="E4" s="3">
         <v>20.0</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="3">
@@ -602,25 +621,25 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="7">
-        <v>3.0</v>
+      <c r="B5" s="6">
+        <v>2.0</v>
       </c>
-      <c r="C5" s="7">
-        <v>7.0</v>
+      <c r="C5" s="6">
+        <v>5.0</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="3">
         <v>20.0</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="3">
         <v>1.0</v>
       </c>
       <c r="H5" s="3"/>
@@ -644,13 +663,27 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="A6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="C6" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="8">
+        <v>20.0</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1.0</v>
+      </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -672,13 +705,27 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="A7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="C7" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="8">
+        <v>20.0</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="8">
+        <v>1.0</v>
+      </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>

--- a/JsonConverter/ExcelFiles/DropTableData.xlsx
+++ b/JsonConverter/ExcelFiles/DropTableData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>아이템 고유 ID</t>
   </si>
@@ -111,6 +111,15 @@
   <si>
     <t>item_deserteagle_diamond_01</t>
   </si>
+  <si>
+    <t>droptable_boss_01</t>
+  </si>
+  <si>
+    <t>item_boss_branch_01</t>
+  </si>
+  <si>
+    <t>item_boss_essence_01</t>
+  </si>
 </sst>
 </file>
 
@@ -204,10 +213,10 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -585,7 +594,7 @@
       <c r="B4" s="1">
         <v>1.0</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="1">
         <v>4.0</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -594,7 +603,7 @@
       <c r="E4" s="3">
         <v>20.0</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="3">
@@ -624,10 +633,10 @@
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="1">
         <v>2.0</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="1">
         <v>5.0</v>
       </c>
       <c r="D5" s="3" t="s">
@@ -663,25 +672,25 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="1">
         <v>4.0</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="1">
         <v>7.0</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="3">
         <v>20.0</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="3">
         <v>1.0</v>
       </c>
       <c r="H6" s="3"/>
@@ -705,25 +714,25 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="1">
         <v>5.0</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="1">
         <v>8.0</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="3">
         <v>20.0</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="3">
         <v>1.0</v>
       </c>
       <c r="H7" s="3"/>
@@ -747,13 +756,27 @@
       <c r="Z7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="A8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="7">
+        <v>100.0</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1000.0</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="8">
+        <v>100.0</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="8">
+        <v>50.0</v>
+      </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
